--- a/artfynd/A 1979-2023 artfynd.xlsx
+++ b/artfynd/A 1979-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134014305</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>99105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134078121</v>
       </c>
       <c r="B3" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134078122</v>
       </c>
       <c r="B4" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134088064</v>
       </c>
       <c r="B5" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1979-2023 artfynd.xlsx
+++ b/artfynd/A 1979-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134014305</v>
       </c>
       <c r="B2" t="n">
-        <v>99105</v>
+        <v>99112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134078121</v>
       </c>
       <c r="B3" t="n">
-        <v>99092</v>
+        <v>99099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134078122</v>
       </c>
       <c r="B4" t="n">
-        <v>99092</v>
+        <v>99099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>134088064</v>
       </c>
       <c r="B5" t="n">
-        <v>99092</v>
+        <v>99099</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1979-2023 artfynd.xlsx
+++ b/artfynd/A 1979-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134014305</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134078121</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134078122</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,8 +1176,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134088064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>